--- a/feature-th-deidentification/CodeSystem-deidentification-action-cs.xlsx
+++ b/feature-th-deidentification/CodeSystem-deidentification-action-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:39:33+00:00</t>
+    <t>2026-09-23T11:46:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/CodeSystem-deidentification-action-cs.xlsx
+++ b/feature-th-deidentification/CodeSystem-deidentification-action-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:46:09+00:00</t>
+    <t>2026-09-23T12:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/CodeSystem-deidentification-action-cs.xlsx
+++ b/feature-th-deidentification/CodeSystem-deidentification-action-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:15:24+00:00</t>
+    <t>2026-09-23T12:19:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/CodeSystem-deidentification-action-cs.xlsx
+++ b/feature-th-deidentification/CodeSystem-deidentification-action-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:19:55+00:00</t>
+    <t>2026-09-23T12:32:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/CodeSystem-deidentification-action-cs.xlsx
+++ b/feature-th-deidentification/CodeSystem-deidentification-action-cs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T12:32:00+00:00</t>
+    <t>2026-09-23T18:28:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature-th-deidentification/CodeSystem-deidentification-action-cs.xlsx
+++ b/feature-th-deidentification/CodeSystem-deidentification-action-cs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://ig.santeon.nl/careplan/CodeSystem/deidentification-action-cs</t>
+    <t>https://ig.santeon.nl/sim-on-fhir/CodeSystem/deidentification-action-cs</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T18:28:14+00:00</t>
+    <t>2026-10-16T14:43:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
